--- a/out/LSTM-Mamba1_repeat_2_000005.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.688844415955534</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.688844415955534</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42277,14 +42277,14 @@
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73282,14 +73282,14 @@
       </c>
       <c r="IZ91" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74872,14 +74872,14 @@
       </c>
       <c r="IZ93" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77257,14 +77257,14 @@
       </c>
       <c r="IZ96" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78847,14 +78847,14 @@
       </c>
       <c r="IZ98" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80437,14 +80437,14 @@
       </c>
       <c r="IZ100" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81232,14 +81232,14 @@
       </c>
       <c r="IZ101" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83617,14 +83617,14 @@
       </c>
       <c r="IZ104" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84412,14 +84412,14 @@
       </c>
       <c r="IZ105" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87592,14 +87592,14 @@
       </c>
       <c r="IZ109" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89182,14 +89182,14 @@
       </c>
       <c r="IZ111" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89977,14 +89977,14 @@
       </c>
       <c r="IZ112" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90772,14 +90772,14 @@
       </c>
       <c r="IZ113" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91567,14 +91567,14 @@
       </c>
       <c r="IZ114" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93157,14 +93157,14 @@
       </c>
       <c r="IZ116" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94747,14 +94747,14 @@
       </c>
       <c r="IZ118" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97132,14 +97132,14 @@
       </c>
       <c r="IZ121" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.111245132341913</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000005.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.088844415955533</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.088844415955533</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.088844415955533</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.711245132341913</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48644,7 +48644,7 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.992350456655223</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.688844415955534</v>
+        <v>-0.1523299884729495</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.711245132341913</v>
+        <v>0.4876904797093241</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.711245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.111245132341913</v>
+        <v>1.127710947891598</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.111245132341913</v>
+        <v>0.9277109478915975</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000005.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01052914932370186</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005869701504707336</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003243536688387394</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001799734309315681</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001067142933607101</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0006556250154972076</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0004006456583738327</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0003555454313755035</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0003657601773738861</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0003614630550146103</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.000315248966217041</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0002810843288898468</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0002402979880571365</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0001870300620794296</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0001294221729040146</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>2.196431159973145e-05</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>8.514523506164551e-05</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0002300087362527847</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>5.627982318401337e-05</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-3.052875399589539e-06</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0002115275710821152</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.0004974044859409332</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.16</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.0006622970104217529</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.0005898419767618179</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.0005341712385416031</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0004614014178514481</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.0003501530736684799</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.0003400035202503204</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.0003216695040464401</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.0002914108335971832</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-4.286691546440125e-05</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.0002158805727958679</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.0004411358386278152</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.0005899369716644287</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.0006698817014694214</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.0006140191107988358</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.0005111675709486008</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.0004081279039382935</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.0003195367753505707</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.0002310015261173248</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.0001695118844509125</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.000168975442647934</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.0001777596771717072</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.0001518018543720245</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0001251921057701111</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0001092422753572464</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-8.209981024265289e-05</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-9.158998727798462e-05</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-7.802806794643402e-05</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-6.088614463806152e-05</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>9.331852197647095e-07</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>1.647323369979858e-05</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-5.749985575675964e-06</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>1.09504908323288e-05</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-3.274343907833099e-05</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>3.567151725292206e-05</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-3.832019865512848e-05</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.1523299884729495</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-8.803978562355042e-05</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.16</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0001400113105773926</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0002242662012577057</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0002449788153171539</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.0002744067460298538</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0002459120005369186</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.0002022087574005127</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0001579765230417252</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-7.795542478561401e-05</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.992350456655223</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-4.958175122737885e-05</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-4.630349576473236e-05</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-1.700781285762787e-05</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-1.012720167636871e-05</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.992350456655223</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-2.894550561904907e-05</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.1523299884729495</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>7.28219747543335e-05</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.4876904797093241</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.0005835145711898804</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.127710947891598</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.0007540266960859299</v>
       </c>
       <c r="JB75" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.001124769449234009</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.001185903325676918</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.001118354499340057</v>
       </c>
       <c r="JB78" t="n">
-        <v>1.127710947891598</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.000920567661523819</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.127710947891598</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0008616950362920761</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.127710947891598</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.0009326506406068802</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.127710947891598</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.001076878979802132</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.127710947891598</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.001368274912238121</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001417925581336021</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.001558411866426468</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.001561528071761131</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.001509405672550201</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.001705273985862732</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001654472202062607</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.001443179324269295</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.001257872208952904</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.00126257911324501</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.001304155215620995</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.16</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.001407062634825706</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.001548618078231812</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.001726498827338219</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.001703964546322823</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.001654310151934624</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.001648858189582825</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.00161292776465416</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.001653693616390228</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.001851353794336319</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.001861168071627617</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.001836454495787621</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.001873541623353958</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.001893360167741776</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.001808490604162216</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.001866430044174194</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.00188751332461834</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.00200355239212513</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.002071605995297432</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.002230944111943245</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.002435436472296715</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.00328291580080986</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.003269832581281662</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.003931386396288872</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003974532708525658</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.003968356177210808</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.003537485376000404</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9277109478915975</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.002825828269124031</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0024238470941782</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97927,14 +97927,14 @@
       </c>
       <c r="IZ122" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.002857936546206474</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98722,14 +98722,14 @@
       </c>
       <c r="IZ123" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.003003228455781937</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99517,14 +99517,14 @@
       </c>
       <c r="IZ124" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.00324070081114769</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100312,14 +100312,14 @@
       </c>
       <c r="IZ125" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0023502167314291</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001753402873873711</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9277109478915975</v>
+        <v>-0.72</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-Mamba1_repeat_2_000005.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01052914932370186</v>
+        <v>-0.01052914280444384</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.005869701504707336</v>
+        <v>-0.005869690328836441</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.003243536688387394</v>
+        <v>-0.003243525512516499</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001799734309315681</v>
+        <v>-0.001799715682864189</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.001067142933607101</v>
+        <v>-0.001067133620381355</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.0006556250154972076</v>
+        <v>-0.000655611976981163</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0004006456583738327</v>
+        <v>-0.0004006437957286835</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0003555454313755035</v>
+        <v>-0.0003555398434400558</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0003657601773738861</v>
+        <v>-0.0003657620400190353</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.0003614630550146103</v>
+        <v>-0.0003614556044340134</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.000315248966217041</v>
+        <v>-0.0003152359277009964</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.0002810843288898468</v>
+        <v>-0.000281069427728653</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.0002402979880571365</v>
+        <v>-0.0002402961254119873</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.0001870300620794296</v>
+        <v>-0.0001870226114988327</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.0001294221729040146</v>
+        <v>-0.00012940913438797</v>
       </c>
       <c r="JB16" t="n">
         <v>0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>2.196431159973145e-05</v>
+        <v>2.197176218032837e-05</v>
       </c>
       <c r="JB17" t="n">
         <v>0.7199999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>8.514523506164551e-05</v>
+        <v>8.515454828739166e-05</v>
       </c>
       <c r="JB18" t="n">
         <v>0.9999999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0002300087362527847</v>
+        <v>0.0002300366759300232</v>
       </c>
       <c r="JB19" t="n">
         <v>0.9999999999999998</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>5.627982318401337e-05</v>
+        <v>5.629844963550568e-05</v>
       </c>
       <c r="JB20" t="n">
         <v>0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-3.052875399589539e-06</v>
+        <v>-3.037974238395691e-06</v>
       </c>
       <c r="JB21" t="n">
         <v>0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.0002115275710821152</v>
+        <v>-0.0002115238457918167</v>
       </c>
       <c r="JB22" t="n">
         <v>0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.0004974044859409332</v>
+        <v>-0.0004973933100700378</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.16</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.0006622970104217529</v>
+        <v>-0.0006622839719057083</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.3</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.0005898419767618179</v>
+        <v>-0.0005898326635360718</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.3</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.0005341712385416031</v>
+        <v>-0.0005341637879610062</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.0004614014178514481</v>
+        <v>-0.0004613902419805527</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.02000000000000007</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.0003501530736684799</v>
+        <v>-0.0003501381725072861</v>
       </c>
       <c r="JB28" t="n">
         <v>0.1199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.0003400035202503204</v>
+        <v>-0.0003400016576051712</v>
       </c>
       <c r="JB29" t="n">
         <v>0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.0002914108335971832</v>
+        <v>-0.0002914071083068848</v>
       </c>
       <c r="JB31" t="n">
         <v>0.9999999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-4.286691546440125e-05</v>
+        <v>-4.286132752895355e-05</v>
       </c>
       <c r="JB32" t="n">
         <v>0.8599999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.0002158805727958679</v>
+        <v>-0.0002158712595701218</v>
       </c>
       <c r="JB33" t="n">
         <v>0.5799999999999998</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.0004411358386278152</v>
+        <v>-0.0004411265254020691</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.0005899369716644287</v>
+        <v>-0.000589931383728981</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.5799999999999998</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.0006698817014694214</v>
+        <v>-0.000669870525598526</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.8599999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.0006140191107988358</v>
+        <v>-0.0006140079349279404</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.9999999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.0005111675709486008</v>
+        <v>-0.0005111545324325562</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.0004081279039382935</v>
+        <v>-0.0004081223160028458</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.0003195367753505707</v>
+        <v>-0.0003195218741893768</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.0002310015261173248</v>
+        <v>-0.0002309773117303848</v>
       </c>
       <c r="JB41" t="n">
         <v>0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.0001695118844509125</v>
+        <v>-0.0001694504171609879</v>
       </c>
       <c r="JB42" t="n">
         <v>0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.000168975442647934</v>
+        <v>-0.0001689363270998001</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.0001777596771717072</v>
+        <v>-0.0001777280122041702</v>
       </c>
       <c r="JB44" t="n">
         <v>0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.0001518018543720245</v>
+        <v>-0.0001517739146947861</v>
       </c>
       <c r="JB45" t="n">
         <v>0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0001251921057701111</v>
+        <v>-0.0001251697540283203</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0001092422753572464</v>
+        <v>-0.0001092348247766495</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-8.209981024265289e-05</v>
+        <v>-8.208677172660828e-05</v>
       </c>
       <c r="JB48" t="n">
         <v>0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-9.158998727798462e-05</v>
+        <v>-9.157881140708923e-05</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-7.802806794643402e-05</v>
+        <v>-7.801875472068787e-05</v>
       </c>
       <c r="JB50" t="n">
         <v>0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-6.088614463806152e-05</v>
+        <v>-6.087683141231537e-05</v>
       </c>
       <c r="JB51" t="n">
         <v>0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>9.331852197647095e-07</v>
+        <v>9.51811671257019e-07</v>
       </c>
       <c r="JB52" t="n">
         <v>0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1.647323369979858e-05</v>
+        <v>1.648440957069397e-05</v>
       </c>
       <c r="JB53" t="n">
         <v>0.3999999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-5.749985575675964e-06</v>
+        <v>-5.738809704780579e-06</v>
       </c>
       <c r="JB54" t="n">
         <v>0.3999999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1.09504908323288e-05</v>
+        <v>1.095235347747803e-05</v>
       </c>
       <c r="JB55" t="n">
         <v>0.3999999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-3.274343907833099e-05</v>
+        <v>-3.27136367559433e-05</v>
       </c>
       <c r="JB56" t="n">
         <v>0.2599999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>3.567151725292206e-05</v>
+        <v>3.569014370441437e-05</v>
       </c>
       <c r="JB57" t="n">
         <v>0.1199999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-3.832019865512848e-05</v>
+        <v>-3.829970955848694e-05</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.02000000000000007</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-8.803978562355042e-05</v>
+        <v>-8.80267471075058e-05</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.16</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0001400113105773926</v>
+        <v>-0.0001399926841259003</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.3</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0002242662012577057</v>
+        <v>-0.0002242457121610641</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.3</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.0002449788153171539</v>
+        <v>-0.0002449583262205124</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.3</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.0002744067460298538</v>
+        <v>-0.0002743899822235107</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.3</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.0002459120005369186</v>
+        <v>-0.0002458933740854263</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.3</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.0002022087574005127</v>
+        <v>-0.0002022013068199158</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.3</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.0001579765230417252</v>
+        <v>-0.0001579653471708298</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-4.958175122737885e-05</v>
+        <v>-4.956498742103577e-05</v>
       </c>
       <c r="JB68" t="n">
         <v>0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-4.630349576473236e-05</v>
+        <v>-4.628673195838928e-05</v>
       </c>
       <c r="JB69" t="n">
         <v>0.5799999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-1.700781285762787e-05</v>
+        <v>-1.701153814792633e-05</v>
       </c>
       <c r="JB70" t="n">
         <v>0.5799999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-1.012720167636871e-05</v>
+        <v>-1.012533903121948e-05</v>
       </c>
       <c r="JB71" t="n">
         <v>0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-2.894550561904907e-05</v>
+        <v>-2.893805503845215e-05</v>
       </c>
       <c r="JB72" t="n">
         <v>0.8599999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>7.28219747543335e-05</v>
+        <v>7.282942533493042e-05</v>
       </c>
       <c r="JB73" t="n">
         <v>0.8599999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.0005835145711898804</v>
+        <v>0.0005835406482219696</v>
       </c>
       <c r="JB74" t="n">
         <v>0.8599999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.0007540266960859299</v>
+        <v>0.0007540639489889145</v>
       </c>
       <c r="JB75" t="n">
         <v>0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.001124769449234009</v>
+        <v>0.001124784350395203</v>
       </c>
       <c r="JB76" t="n">
         <v>0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.001185903325676918</v>
+        <v>0.00118592195212841</v>
       </c>
       <c r="JB77" t="n">
         <v>0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.001118354499340057</v>
+        <v>0.001118378713726997</v>
       </c>
       <c r="JB78" t="n">
         <v>0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.000920567661523819</v>
+        <v>0.0009206105023622513</v>
       </c>
       <c r="JB79" t="n">
         <v>0.8599999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.0008616950362920761</v>
+        <v>0.0008617229759693146</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1199999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.0009326506406068802</v>
+        <v>0.0009326767176389694</v>
       </c>
       <c r="JB81" t="n">
         <v>0.1199999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.001076878979802132</v>
+        <v>0.001076899468898773</v>
       </c>
       <c r="JB82" t="n">
         <v>0.1199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.001368274912238121</v>
+        <v>0.001368304714560509</v>
       </c>
       <c r="JB83" t="n">
         <v>0.1199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.001417925581336021</v>
+        <v>0.001417957246303558</v>
       </c>
       <c r="JB84" t="n">
         <v>0.2599999999999998</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.001558411866426468</v>
+        <v>0.001558415591716766</v>
       </c>
       <c r="JB85" t="n">
         <v>0.3999999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.001561528071761131</v>
+        <v>0.001561544835567474</v>
       </c>
       <c r="JB86" t="n">
         <v>0.9999999999999998</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.001509405672550201</v>
+        <v>0.001509426161646843</v>
       </c>
       <c r="JB87" t="n">
         <v>0.9999999999999998</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.001705273985862732</v>
+        <v>0.001705287024378777</v>
       </c>
       <c r="JB88" t="n">
         <v>0.8599999999999999</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.001654472202062607</v>
+        <v>0.001654498279094696</v>
       </c>
       <c r="JB89" t="n">
         <v>0.7199999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.001443179324269295</v>
+        <v>0.001443205401301384</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.001257872208952904</v>
+        <v>0.001257915049791336</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.16</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.00126257911324501</v>
+        <v>0.001262599602341652</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.001304155215620995</v>
+        <v>0.001304179430007935</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.001407062634825706</v>
+        <v>0.0014070775359869</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.02000000000000007</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.001548618078231812</v>
+        <v>0.001548638567328453</v>
       </c>
       <c r="JB95" t="n">
         <v>0.1199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.001726498827338219</v>
+        <v>0.001726513728499413</v>
       </c>
       <c r="JB96" t="n">
         <v>0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.001703964546322823</v>
+        <v>0.001703953370451927</v>
       </c>
       <c r="JB97" t="n">
         <v>0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.001654310151934624</v>
+        <v>0.001654325053095818</v>
       </c>
       <c r="JB98" t="n">
         <v>0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.001648858189582825</v>
+        <v>0.001648902893066406</v>
       </c>
       <c r="JB99" t="n">
         <v>0.8599999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.00161292776465416</v>
+        <v>0.001612979918718338</v>
       </c>
       <c r="JB100" t="n">
         <v>0.8599999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.001653693616390228</v>
+        <v>0.001653745770454407</v>
       </c>
       <c r="JB101" t="n">
         <v>0.8599999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.001851353794336319</v>
+        <v>0.001851344481110573</v>
       </c>
       <c r="JB102" t="n">
         <v>0.8599999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.001861168071627617</v>
+        <v>0.00186118483543396</v>
       </c>
       <c r="JB103" t="n">
         <v>0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.001873541623353958</v>
+        <v>0.001873563975095749</v>
       </c>
       <c r="JB105" t="n">
         <v>0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.001893360167741776</v>
+        <v>0.001893356442451477</v>
       </c>
       <c r="JB106" t="n">
         <v>0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.001808490604162216</v>
+        <v>0.001808524131774902</v>
       </c>
       <c r="JB107" t="n">
         <v>0.2599999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.001866430044174194</v>
+        <v>0.001866485923528671</v>
       </c>
       <c r="JB108" t="n">
         <v>0.2599999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.00188751332461834</v>
+        <v>0.001887565478682518</v>
       </c>
       <c r="JB109" t="n">
         <v>0.2599999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.00200355239212513</v>
+        <v>0.002003604546189308</v>
       </c>
       <c r="JB110" t="n">
         <v>0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.002071605995297432</v>
+        <v>0.00207165814936161</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.002435436472296715</v>
+        <v>0.002435451373457909</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.00328291580080986</v>
+        <v>0.003282919526100159</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.003269832581281662</v>
+        <v>0.003269821405410767</v>
       </c>
       <c r="JB115" t="n">
         <v>0.9999999999999998</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.003931386396288872</v>
+        <v>0.003931304439902306</v>
       </c>
       <c r="JB116" t="n">
         <v>0.9999999999999998</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.003974532708525658</v>
+        <v>0.003974514082074165</v>
       </c>
       <c r="JB117" t="n">
         <v>0.9999999999999998</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.003968356177210808</v>
+        <v>0.003968285396695137</v>
       </c>
       <c r="JB118" t="n">
         <v>0.2599999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.003537485376000404</v>
+        <v>0.003537422046065331</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.002825828269124031</v>
+        <v>0.002825809642672539</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.0024238470941782</v>
+        <v>0.002423858270049095</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.002857936546206474</v>
+        <v>0.0028579942882061</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.3</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.003003228455781937</v>
+        <v>0.003003271296620369</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.3</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.00324070081114769</v>
+        <v>0.003240706399083138</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.0023502167314291</v>
+        <v>0.002350259572267532</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5800000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.001753402873873711</v>
+        <v>0.001753421500325203</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.72</v>
